--- a/AT/CatSplat UQ Calculator.xlsx
+++ b/AT/CatSplat UQ Calculator.xlsx
@@ -5,17 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wellspan-my.sharepoint.com/personal/dsmith14_wellspan_org/Documents/Documents/GitHub/dps/AT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsmith14\OneDrive - WellSpan Health\Documents\GitHub\dps\AT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="11_0C634D029A174C53F0972CE819298C7321EF0523" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53E3DA45-2F27-4221-B248-431F17D1D70A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BACFE67-3849-4072-8518-5544DBBE48BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="945" yWindow="195" windowWidth="27210" windowHeight="15195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Cold" sheetId="1" r:id="rId1"/>
+    <sheet name="light" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="53">
   <si>
     <t>CatSplat's Differential Cut Underquilt Calculator V0.2 (Beta)</t>
   </si>
@@ -369,7 +368,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -422,19 +421,25 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="4" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -620,6 +625,201 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2038350" cy="3048000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="image1.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BC3A839-CA39-4D6E-B251-DE88475967CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="447675" y="5095875"/>
+          <a:ext cx="2038350" cy="3048000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2000250</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2266950" cy="2114550"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="image4.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD48FEBE-330B-494E-9C6A-0E0D40C66312}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2295525" y="5543550"/>
+          <a:ext cx="2266950" cy="2114550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>381000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="7143750" cy="952500"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="image2.gif">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF79C679-8764-451F-AEC7-7AC9F0E8D547}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5591175" y="5514975"/>
+          <a:ext cx="7143750" cy="952500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1485900</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>342900</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5029200" cy="2905125"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="image3.gif">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BDD6B43-4086-442C-BDDC-C5F0A3F158CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6705600" y="7200900"/>
+          <a:ext cx="5029200" cy="2905125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>371475</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5838825" cy="3724275"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="image5.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33A2ACD8-9B66-4557-8418-D7A456220187}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15325725" y="1314450"/>
+          <a:ext cx="5838825" cy="3724275"/>
+        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -958,12 +1158,13 @@
     <col min="2" max="2" width="39" customWidth="1"/>
     <col min="3" max="3" width="11.140625" customWidth="1"/>
     <col min="4" max="5" width="8.140625" customWidth="1"/>
-    <col min="6" max="6" width="7.42578125" customWidth="1"/>
+    <col min="6" max="6" width="2.28515625" customWidth="1"/>
     <col min="7" max="7" width="41.140625" customWidth="1"/>
     <col min="8" max="8" width="9.140625" customWidth="1"/>
     <col min="9" max="9" width="9.28515625" customWidth="1"/>
     <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="12" width="8.140625" customWidth="1"/>
+    <col min="11" max="11" width="8.140625" customWidth="1"/>
+    <col min="12" max="12" width="2.28515625" customWidth="1"/>
     <col min="13" max="13" width="29.7109375" customWidth="1"/>
     <col min="14" max="14" width="8" customWidth="1"/>
     <col min="15" max="15" width="30" customWidth="1"/>
@@ -972,14 +1173,14 @@
   <sheetData>
     <row r="1" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
     </row>
     <row r="3" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
@@ -987,14 +1188,14 @@
       </c>
     </row>
     <row r="4" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
     </row>
     <row r="5" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="2:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
@@ -1004,18 +1205,18 @@
       <c r="G6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="M6" s="32" t="s">
+      <c r="M6" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="N6" s="31"/>
+      <c r="N6" s="35"/>
     </row>
     <row r="7" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F7" s="33" t="s">
+      <c r="F7" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
     </row>
     <row r="8" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="4"/>
@@ -1356,11 +1557,11 @@
     <row r="25" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="33" t="s">
+      <c r="C27" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
     </row>
     <row r="28" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="29"/>
@@ -1385,12 +1586,12 @@
       <c r="G34" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="31"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
     </row>
     <row r="35" spans="4:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="29"/>
@@ -1505,73 +1706,561 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D53BA0A7-AA6C-48A0-9FDC-AC2955F2992B}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="B1:O67"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="6" width="8.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.42578125" style="30" customWidth="1"/>
+    <col min="2" max="2" width="39" style="30" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" style="30" customWidth="1"/>
+    <col min="4" max="5" width="8.140625" style="30" customWidth="1"/>
+    <col min="6" max="6" width="2.85546875" style="30" customWidth="1"/>
+    <col min="7" max="7" width="41.140625" style="30" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="30" customWidth="1"/>
+    <col min="9" max="9" width="9.28515625" style="30" customWidth="1"/>
+    <col min="10" max="10" width="6" style="30" customWidth="1"/>
+    <col min="11" max="11" width="8.140625" style="30" customWidth="1"/>
+    <col min="12" max="12" width="3.140625" style="30" customWidth="1"/>
+    <col min="13" max="13" width="29.7109375" style="30" customWidth="1"/>
+    <col min="14" max="14" width="8" style="30" customWidth="1"/>
+    <col min="15" max="15" width="30" style="30" customWidth="1"/>
+    <col min="16" max="16" width="85.7109375" style="30" customWidth="1"/>
+    <col min="17" max="16384" width="12.5703125" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+    </row>
+    <row r="3" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+    </row>
+    <row r="5" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="2:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M6" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="N6" s="35"/>
+    </row>
+    <row r="7" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F7" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+    </row>
+    <row r="8" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="4"/>
+      <c r="M8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N8" s="5">
+        <f>H21/H20</f>
+        <v>1.3750000000000001E-3</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="10">
+        <v>78</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="G9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="9">
+        <f>C9</f>
+        <v>78</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="9">
+        <f>C10</f>
+        <v>48</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N9" s="5">
+        <f>(C12+C11)/2</f>
+        <v>1.75</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="10">
+        <v>48</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="G10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="11">
+        <f>C10/C13</f>
+        <v>4.8</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N10" s="5">
+        <f>(C14/850)</f>
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="M11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N11" s="5">
+        <f>N8*N9*N10</f>
+        <v>2.2647058823529417E-3</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="13">
+        <v>2</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="G12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="9">
+        <f>C9</f>
+        <v>78</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="14">
+        <f>H13*C13+(C11*2)</f>
+        <v>57.459307033117419</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" s="15">
+        <f>-17389.0897965567*N11+69.1893383835</f>
+        <v>29.808164432474527</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="24">
+        <v>10</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="G13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="11">
+        <f>(SQRT(((H10/2)^2+(C12-C11)^2)*2)/2)*PI()</f>
+        <v>5.4459307033117419</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="24">
+        <v>800</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="N14" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O14" s="18" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="19">
+        <v>0.1</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="G15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="20">
+        <f>(PI()*H10*(C12-C11)*2/4)/2+(C11*H10)</f>
+        <v>9.0849555921538752</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="N15" s="22">
+        <v>1.8132075754459999E-3</v>
+      </c>
+      <c r="O15" s="18">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="23"/>
+      <c r="M16" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="N16" s="22">
+        <v>1.6972701621560001E-3</v>
+      </c>
+      <c r="O16" s="18">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="4"/>
+      <c r="G17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="20">
+        <f>H15*C9</f>
+        <v>708.62653618800232</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M17" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="N17" s="22">
+        <v>2.8546125094480001E-3</v>
+      </c>
+      <c r="O17" s="18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="24">
+        <v>0.9</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="G18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="25">
+        <f>H21/C13</f>
+        <v>0.97436148725850324</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M18" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="N18" s="22">
+        <v>2.9967017335619998E-3</v>
+      </c>
+      <c r="O18" s="18">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="24">
+        <v>0.67</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="H19" s="26"/>
+      <c r="M19" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="N19" s="22">
+        <v>3.8061500125979998E-3</v>
+      </c>
+      <c r="O19" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="23"/>
+      <c r="G20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20" s="27">
+        <f>H17*C13</f>
+        <v>7086.2653618800232</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M20" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N20" s="22">
+        <v>4.2358458899919996E-3</v>
+      </c>
+      <c r="O20" s="18">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" s="25">
+        <f>(H20/C14)*(1+C15)</f>
+        <v>9.7436148725850327</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H22" s="26"/>
+    </row>
+    <row r="23" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H23" s="28">
+        <f>((H9*J9)+(H12*J12))*C18*0.000771604938*1.15+H21+(C11*C9*(C13-1))*0.000771604938*C19*1.15</f>
+        <v>16.938882120656903</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+    </row>
+    <row r="28" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D28" s="29"/>
+    </row>
+    <row r="29" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D29" s="29"/>
+    </row>
+    <row r="30" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D30" s="29"/>
+    </row>
+    <row r="31" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D31" s="29"/>
+    </row>
+    <row r="32" spans="2:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D32" s="29"/>
+    </row>
+    <row r="33" spans="4:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D33" s="29"/>
+    </row>
+    <row r="34" spans="4:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D34" s="29"/>
+      <c r="G34" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
+    </row>
+    <row r="35" spans="4:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D35" s="29"/>
+    </row>
+    <row r="36" spans="4:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D36" s="29"/>
+    </row>
+    <row r="37" spans="4:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D37" s="29"/>
+    </row>
+    <row r="38" spans="4:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D38" s="29"/>
+    </row>
+    <row r="39" spans="4:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D39" s="29"/>
+    </row>
+    <row r="40" spans="4:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D40" s="29"/>
+    </row>
+    <row r="41" spans="4:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D41" s="29"/>
+    </row>
+    <row r="42" spans="4:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D42" s="29"/>
+    </row>
+    <row r="43" spans="4:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D43" s="29"/>
+    </row>
+    <row r="44" spans="4:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D44" s="29"/>
+    </row>
+    <row r="45" spans="4:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D45" s="29"/>
+    </row>
+    <row r="46" spans="4:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D46" s="29"/>
+    </row>
+    <row r="47" spans="4:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D47" s="29"/>
+    </row>
+    <row r="48" spans="4:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D48" s="29"/>
+    </row>
+    <row r="49" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D49" s="29"/>
+    </row>
+    <row r="50" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D50" s="29"/>
+    </row>
+    <row r="51" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D51" s="29"/>
+    </row>
+    <row r="52" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D52" s="29"/>
+    </row>
+    <row r="53" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D53" s="29"/>
+    </row>
+    <row r="54" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D54" s="29"/>
+    </row>
+    <row r="55" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D55" s="29"/>
+    </row>
+    <row r="56" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D56" s="29"/>
+    </row>
+    <row r="57" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D57" s="29"/>
+    </row>
+    <row r="58" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D58" s="29"/>
+    </row>
+    <row r="59" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D59" s="29"/>
+    </row>
+    <row r="60" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D60" s="29"/>
+    </row>
+    <row r="61" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D61" s="29"/>
+    </row>
+    <row r="62" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D62" s="29"/>
+    </row>
+    <row r="63" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D63" s="29"/>
+    </row>
+    <row r="64" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D64" s="29"/>
+    </row>
+    <row r="65" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D65" s="29"/>
+    </row>
+    <row r="66" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D66" s="29"/>
+    </row>
+    <row r="67" spans="4:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D67" s="29"/>
+    </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="G34:M34"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:A20"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="6" width="8.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>